--- a/tools/final_results/assets/classification-results-spreadsheet-template.xlsx
+++ b/tools/final_results/assets/classification-results-spreadsheet-template.xlsx
@@ -420,14 +420,16 @@
   <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32.83203125" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15.1640625" customWidth="1" min="3" max="3"/>
-    <col width="11.33203125" customWidth="1" min="5" max="5"/>
-    <col width="31.33203125" customWidth="1" min="6" max="6"/>
-    <col width="18.83203125" customWidth="1" min="7" max="7"/>
-    <col width="15.1640625" customWidth="1" min="9" max="9"/>
-    <col width="15.1640625" customWidth="1" min="10" max="10"/>
+    <col width="24.5" customWidth="1" min="1" max="1"/>
+    <col width="29.5" customWidth="1" min="2" max="2"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
+    <col width="8.5" customWidth="1" min="4" max="4"/>
+    <col width="8.5" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+    <col width="20.5" customWidth="1" min="8" max="8"/>
+    <col width="12.5" customWidth="1" min="9" max="9"/>
+    <col width="8.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1720,14 +1722,16 @@
   <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32.83203125" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15.1640625" customWidth="1" min="3" max="3"/>
-    <col width="11.33203125" customWidth="1" min="5" max="5"/>
-    <col width="31.33203125" customWidth="1" min="6" max="6"/>
-    <col width="18.83203125" customWidth="1" min="7" max="7"/>
-    <col width="15.1640625" customWidth="1" min="9" max="9"/>
-    <col width="15.1640625" customWidth="1" min="10" max="10"/>
+    <col width="24.5" customWidth="1" min="1" max="1"/>
+    <col width="29.5" customWidth="1" min="2" max="2"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
+    <col width="8.5" customWidth="1" min="4" max="4"/>
+    <col width="8.5" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+    <col width="20.5" customWidth="1" min="8" max="8"/>
+    <col width="12.5" customWidth="1" min="9" max="9"/>
+    <col width="8.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3020,14 +3024,16 @@
   <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32.83203125" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15.1640625" customWidth="1" min="3" max="3"/>
-    <col width="11.33203125" customWidth="1" min="5" max="5"/>
-    <col width="31.33203125" customWidth="1" min="6" max="6"/>
-    <col width="18.83203125" customWidth="1" min="7" max="7"/>
-    <col width="15.1640625" customWidth="1" min="9" max="9"/>
-    <col width="15.1640625" customWidth="1" min="10" max="10"/>
+    <col width="24.5" customWidth="1" min="1" max="1"/>
+    <col width="29.5" customWidth="1" min="2" max="2"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
+    <col width="8.5" customWidth="1" min="4" max="4"/>
+    <col width="8.5" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+    <col width="20.5" customWidth="1" min="8" max="8"/>
+    <col width="12.5" customWidth="1" min="9" max="9"/>
+    <col width="8.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4320,14 +4326,16 @@
   <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32.83203125" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15.1640625" customWidth="1" min="3" max="3"/>
-    <col width="11.33203125" customWidth="1" min="5" max="5"/>
-    <col width="31.33203125" customWidth="1" min="6" max="6"/>
-    <col width="18.83203125" customWidth="1" min="7" max="7"/>
-    <col width="15.1640625" customWidth="1" min="9" max="9"/>
-    <col width="15.1640625" customWidth="1" min="10" max="10"/>
+    <col width="24.5" customWidth="1" min="1" max="1"/>
+    <col width="29.5" customWidth="1" min="2" max="2"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
+    <col width="8.5" customWidth="1" min="4" max="4"/>
+    <col width="8.5" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+    <col width="20.5" customWidth="1" min="8" max="8"/>
+    <col width="12.5" customWidth="1" min="9" max="9"/>
+    <col width="8.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
